--- a/资料包/物品清单.xlsx
+++ b/资料包/物品清单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RAS\Fast-Drone-250\电赛uav\UAV\资料包\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAB60B8-9F01-48F9-9A15-00A70921BFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27913876-AD86-48F9-B2EF-047C4B1B13B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="336" yWindow="1908" windowWidth="27612" windowHeight="14436" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -333,6 +333,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -340,9 +343,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -713,7 +713,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -731,13 +731,13 @@
       <c r="F4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>41</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
+      <c r="A5" s="4"/>
       <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
@@ -753,7 +753,7 @@
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="3"/>
+      <c r="G5" s="4"/>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -776,7 +776,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="2"/>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>55</v>
       </c>
     </row>
@@ -798,7 +798,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="5"/>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
@@ -889,7 +889,7 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -906,12 +906,12 @@
         <v>10</v>
       </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
+      <c r="A13" s="4"/>
       <c r="B13" s="2" t="s">
         <v>34</v>
       </c>
@@ -946,7 +946,7 @@
         <v>10</v>
       </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="3" t="s">
         <v>55</v>
       </c>
     </row>

--- a/资料包/物品清单.xlsx
+++ b/资料包/物品清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RAS\Fast-Drone-250\电赛uav\UAV\资料包\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27913876-AD86-48F9-B2EF-047C4B1B13B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A2923B-327B-4A40-BBCD-4F02B13C11D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="336" yWindow="1908" windowWidth="27612" windowHeight="14436" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1764" windowWidth="27612" windowHeight="14436" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
   <si>
     <t>类目</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -191,10 +191,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>可白嫖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>不包括地面端</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -235,6 +231,14 @@
   </si>
   <si>
     <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~1k</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -661,7 +665,7 @@
         <v>40</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -709,7 +713,7 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -777,7 +781,7 @@
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -836,14 +840,14 @@
         <v>84</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -860,7 +864,7 @@
         <v>450</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>10</v>
@@ -870,10 +874,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
@@ -907,7 +911,7 @@
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -918,12 +922,14 @@
       <c r="C13" s="2">
         <v>1</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="F13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -931,7 +937,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
@@ -940,22 +946,22 @@
         <v>250</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
@@ -964,14 +970,14 @@
         <v>144</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -991,7 +997,7 @@
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1012,10 +1018,10 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">

--- a/资料包/物品清单.xlsx
+++ b/资料包/物品清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RAS\Fast-Drone-250\电赛uav\UAV\资料包\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A2923B-327B-4A40-BBCD-4F02B13C11D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68783D30-2490-4B11-8739-C0C012CF00FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1764" windowWidth="27612" windowHeight="14436" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3384" yWindow="3384" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
   <si>
     <t>类目</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -62,183 +62,169 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电调</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EMAX银燕 BLHELI32 45A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?abbucket=7&amp;id=683545520078&amp;ns=1&amp;pisk=fwuIKfmma9XBfYdUx_dafF0kPU4PPYTVd_N-ibQFwyULecGmFJRkxyo_FAH_pwRHxueSKyEoY8yUFzGohD92uElntzqJ3K82QEtzLyFL97eJw5Fzge9wbOlntz4J3K82uXj5UJzNJ7eJ1FF8gzB897d_X7VzywERJGBTIRe8ykeLX1FuagBLpad1XWVlvaFL9lhTZSX8yzH-6XaP57KQMXOTj3yvOL9xNR_RljVYXtGG4ZQvNWrLHE2fy5u_OkwxT2mPl1Nt7VZ4b_J7WjmZp5aX7MUx10HjDYxVjyG-vYqsKdj_QcnZw8EA9wUI2v07xD1kifUKIm20vhvg12u4V-q1dZwr-vu_cqpO55cZg2qiPK6TEDP0WSlHRNax97IymZyjtEs51ob81MA61gjktVgBdt7-EKELsW921C6hqtbRzG0y1gIUv5VI9CO1KT1..&amp;priceTId=2147812c17260326030733593e1c62&amp;skuId=4892210053424&amp;spm=a21n57.1.item.49.6df6523cnwQHX4&amp;utparam=%7B%22aplus_abtest%22:%229744b18383478e2a547522911a87a0ff%22%7D</t>
+  </si>
+  <si>
+    <t>桨叶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乾丰碳纤尼龙9047（正反一对）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?id=588756823324&amp;pvid=77abd789-c8b2-4b4e-8b47-14e06ec9cfb6&amp;scm=1007.10157.81291.100200300000000&amp;skuId=4012713700889&amp;spm=a1z02.1.guess_item.d2</t>
+  </si>
+  <si>
+    <t>飞控</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷迅V5nano</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?abbucket=7&amp;id=726447702072&amp;ns=1&amp;pisk=fZ6SppfGY40SVcryZDE2G-xU5EvFewwZPDtdjMHrvLpJJssGRUr3ZL5XRZQXyYruZBLCrLdhae8yRpsh5_aaQRSlqpAL7PyZaQrjgd0K2v3eDnKwZrrquRSlqpvL7PyaQXOWk1H-9eQLHEK6k23JywdxHHYxeHHJvqEXoHppv3K8HEKpY4Kp2w3vMhttp4HJpIIvXHJpJwpK_UDXv7tOVod0EVRsRYXJlvH1jeRY8_lEnxjy2QGkNEt20ttWNFR4m10GeZSdUTA0tXJh01_C9wVZiLsdwLKNq8MXBgCVdnWUYXTR0tsAdCiLXFBlDOvvgRE1DtbPqtsEvJKV7EIled3YKnXPvTOCdyGHU1SNKCB8FVY2sH_yuNethKdd4KDw5g2sOmOipnGucoGntuXfFzgZpw49wnx77oZjrX0ipvlcLoGKaQKDVgEbc40C.&amp;priceTId=2147bf7717260337245795269e5f35&amp;skuId=5050156296398&amp;spm=a21n57.1.item.48.1934523cy3IJc2&amp;utparam=%7B%22aplus_abtest%22:%22cc02f591c24599d5c7b98d1b4f65c85e%22%7D</t>
+  </si>
+  <si>
+    <t>动力电池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格式4S 2300mAh 45C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?id=533911258121&amp;pisk=fzWiNec7i1R6snWS2Wv_MX1PCYF-5c9X0ZHvkKL4Te8BM1HOXZfhVZYTc59OtEbF-FWT1EHmowSxXCRw7Hyem3hwuxJVtmj5-ZAbfEL2oZIV6128eGs6hK80y8e8jVKhxNmwgArqLnx-pfXjDGs6hKz8y8eRfj0v0_GMgZyETnLe0c-NupSeqekw0AJ28kxXJuc-VwZVUlvMrVmAyUqu_STlbeDoA9xElU2W8x-NLhRi1OLhvMBHjCYJ9voVgO7d0OB6O-D2hMClos7bwX9G01Jw2GwiKLSN9txdHohD7MBhYtAo0u8PCMWWLBezqMWCWG6hDmy2vaLFfOJr8-tCBiWMit4mGgyKTblKnxtUD9cj9C-BxUdd8T_Vjr7O4kqnNsOwA3YRHkcq64MqHXZ3xbZD_Htk7&amp;spm=a1z10.5-c-s.w4002-14528659934.11.16117de1Hzy5Je&amp;skuId=4139317346484</t>
+  </si>
+  <si>
+    <t>电源模块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷迅HV PM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doc.cuav.net/power-module/zh-hans/hv-pm.html</t>
+  </si>
+  <si>
+    <t>接收机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乐迪R12DSM 2.4G 12通道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遥控</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乐迪AT9S PRO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>相机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Intel T265</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D435</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>降压模块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC-DC降压 5V1.6A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图传</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OpenIPC ssc338+imx415+rtl8812au</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不包括地面端</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乐动LD14P 二维雷达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>光流&amp;激光测距</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>微空科技MTF-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>机载电脑</t>
+  </si>
+  <si>
+    <t>Intel NUC11TNKi5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?abbucket=7&amp;id=541658831753&amp;ns=1&amp;pisk=fM8qpN4ehq3q6Ounhs7NaYBeEbSvQZDIuF61sCAGGtXchCfG7LvsMtOiHd8NECKjMGMY_SLyLPajHmdg7w_idvgIRIdfWNDQGGJMR-CFtO01no0oh7bZPvgIRIdAWNDIdfn-ZmCGOPbgmt2oas10nNjGiQcPs1w0jrviaQXR1oq0mtXlq6f_mNfcIaqlOs2goi40rTXRsNqm9aYMuzWVmXkKgKLKc2y5LIXz87BOZusxJa4ixUf4djOVU_1WzsSVdgGJvJLDFCYXkgnTfNdWYd-MBDZRuCxco6Oxuz7Hi3TNNFG_btAWzQYNY5chKEdkJajS-XRkyKOvzCNiS_9CEILc-80OwEOMuG8ZQlQXABTOxE04pTsd_K6WK24PrGjyCRCuMoY90RqGmP1PdblyteJosp_GUQZTXgcRa9GETlqgpya_0FGYXlIkQ_WITjC..&amp;priceTId=2147823417260347080721506ec336&amp;skuId=3642863966624&amp;spm=a21n57.1.item.272.1934523cy3IJc2&amp;utparam=%7B%22aplus_abtest%22:%22e2de6ce3eafd44b7b982b485c42f9d55%22%7D</t>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?abbucket=7&amp;id=612126103740&amp;ns=1&amp;pisk=fPQspxslgADsT5NwjjFeAyA4FpY27tarCjOAZs3ZMFL9HM1lhdP0jFSBh9BBBVPgjnpfIFKcbKJwhE1cFGwzzz5GsExYU8zrbhPIYUmxDnHqJDdWjJPELz5GsEYYU8zzzmt6tLgtDKBYJpdJpfdxXtKKJIvKWI39MvFBKILvMCdTJpdvgAdv6tnpJIOXMmK9kpHpZILvHtLxtNuBMlOR1WK3SY-7V7UXpq3AWEXHh2WHth7QJhp56mSFxwgkfLC9dqy-xJy6hpb8Lk1hQGBwtta7dEXhDtdfpve2jsICdC6aFxvVS17Xt1ZTh_T1AwTNW-mlT699VeSUxR-25OskEhE3KTK5ag8GyJgJhGBGn3b4EVvOM_bl4UaEXUCCDTsf4K0yF14ScXtokBigOWimm5bC5RMrkt2JXBA_UWNIImDokqohuWixbhdH11FQOADf.&amp;priceTId=2147817217260370261762292e7d0b&amp;skuId=4476709986453&amp;spm=a21n57.1.item.317.1934523cy3IJc2&amp;utparam=%7B%22aplus_abtest%22:%2266f295335b31d912c105a897fefba037%22%7D</t>
+  </si>
+  <si>
+    <t>https://detail.tmall.com/item.htm?abbucket=7&amp;id=645324033043&amp;ns=1&amp;pisk=fgMjKZGnbZbj0B-4iGKzNLqwRz2aN3k6LESsxDUN31exPPUSvn42sI0sNV3ugrU2mRNtWq3_sn4aWPgZXjlXLpommR2T5eJeLdF4r_gf6SCvXuE_cKTyaaommR298eJeLmf17uQFHlU9VLETxRIYXrK7wkrTBtFOH_Q8rzUTB5EAeLETjlQY6oK5wkqCHlUTBzU8jkBYBR3TeXyAFldbvmt8ZKbUOaLF4zXOBxeM3yi53KmKWo6u8ma7qFH8cw4KDz6OQrYDUBnS0E6n4-DqRku2etgIxY0722p6PR0o6VEsypbanXumK7g29TnLCrgT1bYCLowqNWMjihb-D2zj9-mNAEo76kM03b8fpyhIDXroQUXY5bht3S2GkePmXbg7cJIyi9zImp11VWXTVsxWV1fMmYMXlwWtSeFYqoTeV3_cswXOQ_DwV1C4MuqjD3t5oN1..&amp;priceTId=2147817217260372266404458e7d0b&amp;skuId=5114463806551&amp;spm=a21n57.1.item.413.1934523cy3IJc2&amp;utparam=%7B%22aplus_abtest%22:%22d2173938c6cf8fb38700f3e44f68a63a%22%7D&amp;xxc=taobaoSearch</t>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?abbucket=7&amp;id=692735724689&amp;ns=1&amp;pisk=fHZrLRtaNgIPm1IGNYoE3shaituRyDPF1QrIKv2LppcoqbaqKWNApTn7KXPUGjK7Pa3ITpo8cztIN_nUK5iN11s1f8e-JDf11UgF3liiCYAHOYcmn4vAhis1f8e-vDf11G6KzofSIex3tUcDijHEtv0utqxmpjxoK3DHitlxKDDnEYjmivDBZvDutEjmLAKkr30nnED-UDc3tDcEmkqy0bulQ1BzwlIWogl_Ej-wHFMoo6M9RIdvMY3osGIyYHWKU4lgEjCsIUsroJ3UvpKEl84T9AVkZ1g8KrPqUDSXrc24-5kYqGOrHzw09j2wUHy43J4suo6GX0ooZyi8dd573uP7eoyBKUPU57Ut8kfybjq8lu3TVsxrjPeSVyVd5EnzKzmV4OOKnLLuvzRH-4xI3f6V3Rqai9VsxjyXJe3cHxl1QO8H-CK6AUrCeeLKoWkq1OWR.&amp;priceTId=2150421c17260374120045602e83e1&amp;skuId=5522133784267&amp;spm=a21n57.1.item.458.1934523cy3IJc2&amp;utparam=%7B%22aplus_abtest%22:%22999529ac7eb943e215e7173313fe3601%22%7D</t>
+  </si>
+  <si>
+    <t>发票</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>N</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>~1k</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>电调</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EMAX银燕 BLHELI32 45A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://item.taobao.com/item.htm?abbucket=7&amp;id=683545520078&amp;ns=1&amp;pisk=fwuIKfmma9XBfYdUx_dafF0kPU4PPYTVd_N-ibQFwyULecGmFJRkxyo_FAH_pwRHxueSKyEoY8yUFzGohD92uElntzqJ3K82QEtzLyFL97eJw5Fzge9wbOlntz4J3K82uXj5UJzNJ7eJ1FF8gzB897d_X7VzywERJGBTIRe8ykeLX1FuagBLpad1XWVlvaFL9lhTZSX8yzH-6XaP57KQMXOTj3yvOL9xNR_RljVYXtGG4ZQvNWrLHE2fy5u_OkwxT2mPl1Nt7VZ4b_J7WjmZp5aX7MUx10HjDYxVjyG-vYqsKdj_QcnZw8EA9wUI2v07xD1kifUKIm20vhvg12u4V-q1dZwr-vu_cqpO55cZg2qiPK6TEDP0WSlHRNax97IymZyjtEs51ob81MA61gjktVgBdt7-EKELsW921C6hqtbRzG0y1gIUv5VI9CO1KT1..&amp;priceTId=2147812c17260326030733593e1c62&amp;skuId=4892210053424&amp;spm=a21n57.1.item.49.6df6523cnwQHX4&amp;utparam=%7B%22aplus_abtest%22:%229744b18383478e2a547522911a87a0ff%22%7D</t>
-  </si>
-  <si>
-    <t>桨叶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>乾丰碳纤尼龙9047（正反一对）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://item.taobao.com/item.htm?id=588756823324&amp;pvid=77abd789-c8b2-4b4e-8b47-14e06ec9cfb6&amp;scm=1007.10157.81291.100200300000000&amp;skuId=4012713700889&amp;spm=a1z02.1.guess_item.d2</t>
-  </si>
-  <si>
-    <t>https://item.taobao.com/item.htm?abbucket=7&amp;id=763888431742&amp;ns=1&amp;pisk=ftEtKl67o6fGoFJCXE_nm7bP_m6oWoeNs5yWmjcMlWFLhXxcQcbqDShLgf0iffxxD-F4iSeVQxGbGSh0S9juQRoqc_cAqg2NcqhC8S3sGvTQLxJshCInbOiqc_flqg2aQmPlLV6K1eMITAK6lST_dJGEnAt_GfgBOYHrcmibG2tIEAK6fqtsRHGEUEt6cn9IdxMv1ngbGJ6K3fWCWXpspnUfo6BmfnRMrUqKdjl8pa8sauHtsbe6oNbG3A3tNRGFZYTGX2wqkoJ2D22_zSk71C1o7-aL9AnAxFi7prN-Llsk6vzgdSlQedKYpJebr2EhFgotffamb-vRsJETsRrLnKTTMzVazqEf63hQbyqZzlfBX0azIc4bgaYEX-asvgrbquh9kQc-nFBLcE8q5v73PhEldGI_OvhlBAL2uqMemFEcQETXa3DKZOdyuEujH&amp;priceTId=215045eb17260329480036424eea8c&amp;skuId=5256458552866&amp;spm=a21n57.1.item.10.1934523cy3IJc2&amp;utparam=%7B%22aplus_abtest%22:%22dd05baa95f2c95bb00adc9eb7cf71216%22%7D</t>
-  </si>
-  <si>
-    <t>乾丰玻纤尼龙9045（正反一对）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>飞控</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷迅V5nano</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://item.taobao.com/item.htm?abbucket=7&amp;id=726447702072&amp;ns=1&amp;pisk=fZ6SppfGY40SVcryZDE2G-xU5EvFewwZPDtdjMHrvLpJJssGRUr3ZL5XRZQXyYruZBLCrLdhae8yRpsh5_aaQRSlqpAL7PyZaQrjgd0K2v3eDnKwZrrquRSlqpvL7PyaQXOWk1H-9eQLHEK6k23JywdxHHYxeHHJvqEXoHppv3K8HEKpY4Kp2w3vMhttp4HJpIIvXHJpJwpK_UDXv7tOVod0EVRsRYXJlvH1jeRY8_lEnxjy2QGkNEt20ttWNFR4m10GeZSdUTA0tXJh01_C9wVZiLsdwLKNq8MXBgCVdnWUYXTR0tsAdCiLXFBlDOvvgRE1DtbPqtsEvJKV7EIled3YKnXPvTOCdyGHU1SNKCB8FVY2sH_yuNethKdd4KDw5g2sOmOipnGucoGntuXfFzgZpw49wnx77oZjrX0ipvlcLoGKaQKDVgEbc40C.&amp;priceTId=2147bf7717260337245795269e5f35&amp;skuId=5050156296398&amp;spm=a21n57.1.item.48.1934523cy3IJc2&amp;utparam=%7B%22aplus_abtest%22:%22cc02f591c24599d5c7b98d1b4f65c85e%22%7D</t>
-  </si>
-  <si>
-    <t>动力电池</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>格式4S 2300mAh 45C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://item.taobao.com/item.htm?id=533911258121&amp;pisk=fzWiNec7i1R6snWS2Wv_MX1PCYF-5c9X0ZHvkKL4Te8BM1HOXZfhVZYTc59OtEbF-FWT1EHmowSxXCRw7Hyem3hwuxJVtmj5-ZAbfEL2oZIV6128eGs6hK80y8e8jVKhxNmwgArqLnx-pfXjDGs6hKz8y8eRfj0v0_GMgZyETnLe0c-NupSeqekw0AJ28kxXJuc-VwZVUlvMrVmAyUqu_STlbeDoA9xElU2W8x-NLhRi1OLhvMBHjCYJ9voVgO7d0OB6O-D2hMClos7bwX9G01Jw2GwiKLSN9txdHohD7MBhYtAo0u8PCMWWLBezqMWCWG6hDmy2vaLFfOJr8-tCBiWMit4mGgyKTblKnxtUD9cj9C-BxUdd8T_Vjr7O4kqnNsOwA3YRHkcq64MqHXZ3xbZD_Htk7&amp;spm=a1z10.5-c-s.w4002-14528659934.11.16117de1Hzy5Je&amp;skuId=4139317346484</t>
-  </si>
-  <si>
-    <t>电源模块</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷迅HV PM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://doc.cuav.net/power-module/zh-hans/hv-pm.html</t>
-  </si>
-  <si>
-    <t>接收机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>乐迪R12DSM 2.4G 12通道</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遥控</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>乐迪AT9S PRO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>相机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Intel T265</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D435</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>降压模块</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DC-DC降压 5V1.6A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>图传</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OpenIPC ssc338+imx415+rtl8812au</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>待购买</t>
-  </si>
-  <si>
-    <t>待购买</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不包括地面端</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>乐动LD14P 二维雷达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>光流&amp;激光测距</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>微空科技MTF-01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>机载电脑</t>
-  </si>
-  <si>
-    <t>Intel NUC11TNKi5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://item.taobao.com/item.htm?abbucket=7&amp;id=541658831753&amp;ns=1&amp;pisk=fM8qpN4ehq3q6Ounhs7NaYBeEbSvQZDIuF61sCAGGtXchCfG7LvsMtOiHd8NECKjMGMY_SLyLPajHmdg7w_idvgIRIdfWNDQGGJMR-CFtO01no0oh7bZPvgIRIdAWNDIdfn-ZmCGOPbgmt2oas10nNjGiQcPs1w0jrviaQXR1oq0mtXlq6f_mNfcIaqlOs2goi40rTXRsNqm9aYMuzWVmXkKgKLKc2y5LIXz87BOZusxJa4ixUf4djOVU_1WzsSVdgGJvJLDFCYXkgnTfNdWYd-MBDZRuCxco6Oxuz7Hi3TNNFG_btAWzQYNY5chKEdkJajS-XRkyKOvzCNiS_9CEILc-80OwEOMuG8ZQlQXABTOxE04pTsd_K6WK24PrGjyCRCuMoY90RqGmP1PdblyteJosp_GUQZTXgcRa9GETlqgpya_0FGYXlIkQ_WITjC..&amp;priceTId=2147823417260347080721506ec336&amp;skuId=3642863966624&amp;spm=a21n57.1.item.272.1934523cy3IJc2&amp;utparam=%7B%22aplus_abtest%22:%22e2de6ce3eafd44b7b982b485c42f9d55%22%7D</t>
-  </si>
-  <si>
-    <t>https://item.taobao.com/item.htm?abbucket=7&amp;id=612126103740&amp;ns=1&amp;pisk=fPQspxslgADsT5NwjjFeAyA4FpY27tarCjOAZs3ZMFL9HM1lhdP0jFSBh9BBBVPgjnpfIFKcbKJwhE1cFGwzzz5GsExYU8zrbhPIYUmxDnHqJDdWjJPELz5GsEYYU8zzzmt6tLgtDKBYJpdJpfdxXtKKJIvKWI39MvFBKILvMCdTJpdvgAdv6tnpJIOXMmK9kpHpZILvHtLxtNuBMlOR1WK3SY-7V7UXpq3AWEXHh2WHth7QJhp56mSFxwgkfLC9dqy-xJy6hpb8Lk1hQGBwtta7dEXhDtdfpve2jsICdC6aFxvVS17Xt1ZTh_T1AwTNW-mlT699VeSUxR-25OskEhE3KTK5ag8GyJgJhGBGn3b4EVvOM_bl4UaEXUCCDTsf4K0yF14ScXtokBigOWimm5bC5RMrkt2JXBA_UWNIImDokqohuWixbhdH11FQOADf.&amp;priceTId=2147817217260370261762292e7d0b&amp;skuId=4476709986453&amp;spm=a21n57.1.item.317.1934523cy3IJc2&amp;utparam=%7B%22aplus_abtest%22:%2266f295335b31d912c105a897fefba037%22%7D</t>
-  </si>
-  <si>
-    <t>https://detail.tmall.com/item.htm?abbucket=7&amp;id=645324033043&amp;ns=1&amp;pisk=fgMjKZGnbZbj0B-4iGKzNLqwRz2aN3k6LESsxDUN31exPPUSvn42sI0sNV3ugrU2mRNtWq3_sn4aWPgZXjlXLpommR2T5eJeLdF4r_gf6SCvXuE_cKTyaaommR298eJeLmf17uQFHlU9VLETxRIYXrK7wkrTBtFOH_Q8rzUTB5EAeLETjlQY6oK5wkqCHlUTBzU8jkBYBR3TeXyAFldbvmt8ZKbUOaLF4zXOBxeM3yi53KmKWo6u8ma7qFH8cw4KDz6OQrYDUBnS0E6n4-DqRku2etgIxY0722p6PR0o6VEsypbanXumK7g29TnLCrgT1bYCLowqNWMjihb-D2zj9-mNAEo76kM03b8fpyhIDXroQUXY5bht3S2GkePmXbg7cJIyi9zImp11VWXTVsxWV1fMmYMXlwWtSeFYqoTeV3_cswXOQ_DwV1C4MuqjD3t5oN1..&amp;priceTId=2147817217260372266404458e7d0b&amp;skuId=5114463806551&amp;spm=a21n57.1.item.413.1934523cy3IJc2&amp;utparam=%7B%22aplus_abtest%22:%22d2173938c6cf8fb38700f3e44f68a63a%22%7D&amp;xxc=taobaoSearch</t>
-  </si>
-  <si>
-    <t>https://item.taobao.com/item.htm?abbucket=7&amp;id=692735724689&amp;ns=1&amp;pisk=fHZrLRtaNgIPm1IGNYoE3shaituRyDPF1QrIKv2LppcoqbaqKWNApTn7KXPUGjK7Pa3ITpo8cztIN_nUK5iN11s1f8e-JDf11UgF3liiCYAHOYcmn4vAhis1f8e-vDf11G6KzofSIex3tUcDijHEtv0utqxmpjxoK3DHitlxKDDnEYjmivDBZvDutEjmLAKkr30nnED-UDc3tDcEmkqy0bulQ1BzwlIWogl_Ej-wHFMoo6M9RIdvMY3osGIyYHWKU4lgEjCsIUsroJ3UvpKEl84T9AVkZ1g8KrPqUDSXrc24-5kYqGOrHzw09j2wUHy43J4suo6GX0ooZyi8dd573uP7eoyBKUPU57Ut8kfybjq8lu3TVsxrjPeSVyVd5EnzKzmV4OOKnLLuvzRH-4xI3f6V3Rqai9VsxjyXJe3cHxl1QO8H-CK6AUrCeeLKoWkq1OWR.&amp;priceTId=2150421c17260374120045602e83e1&amp;skuId=5522133784267&amp;spm=a21n57.1.item.458.1934523cy3IJc2&amp;utparam=%7B%22aplus_abtest%22:%22999529ac7eb943e215e7173313fe3601%22%7D</t>
-  </si>
-  <si>
-    <t>发票</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>~1k</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -629,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
@@ -662,10 +648,10 @@
         <v>8</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -687,17 +673,17 @@
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="C3" s="2">
         <v>4</v>
@@ -706,22 +692,22 @@
         <v>230.48</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="C4" s="2">
         <v>2</v>
@@ -730,316 +716,294 @@
         <v>6.8</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
       <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>899</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2">
-        <v>27.8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="5" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="2">
-        <v>899</v>
-      </c>
+      <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" s="2"/>
-      <c r="H6" s="5" t="s">
-        <v>54</v>
-      </c>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>148</v>
+      </c>
       <c r="E7" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="6"/>
+      <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="C9" s="2">
         <v>1</v>
       </c>
       <c r="D9" s="2">
-        <v>84</v>
+        <v>450</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C10" s="2">
         <v>1</v>
       </c>
       <c r="D10" s="2">
-        <v>450</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>50</v>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>47</v>
+      <c r="A11" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2">
         <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>2000</v>
+        <v>1960</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="H11" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="A12" s="4"/>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
       </c>
-      <c r="D12" s="2">
-        <v>1960</v>
+      <c r="D12" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="3" t="s">
-        <v>54</v>
-      </c>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2">
         <v>1</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="2"/>
+      <c r="D13" s="2">
+        <v>250</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="H13" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>250</v>
+        <v>144</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="3" t="s">
-        <v>54</v>
+      <c r="H14" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
       </c>
-      <c r="D15" s="2">
-        <v>144</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="C16" s="2">
         <v>1</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" s="2">
+        <v>568</v>
+      </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="H16" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="2">
-        <v>1</v>
-      </c>
-      <c r="D17" s="2">
-        <v>568</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H6:H7"/>
+  <mergeCells count="2">
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
